--- a/data/obx_xlsx/KOMPLK.OL.xlsx
+++ b/data/obx_xlsx/KOMPLK.OL.xlsx
@@ -8248,13 +8248,27 @@
       <c r="J34" s="16">
         <v>65.65</v>
       </c>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
+      <c r="K34" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="L34" s="16">
+        <v>19.42</v>
+      </c>
+      <c r="M34" s="16">
+        <v>49.86</v>
+      </c>
+      <c r="N34" s="16">
+        <v>31.5</v>
+      </c>
+      <c r="O34" s="15">
+        <v>153.98</v>
+      </c>
+      <c r="P34" s="15">
+        <v>166.47</v>
+      </c>
+      <c r="Q34" s="15">
+        <v>206.03</v>
+      </c>
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
